--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/10,08,26 Останкино КИ и ЗПФ/дв 10,08,26 бррсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/10,08,26 Останкино КИ и ЗПФ/дв 10,08,26 бррсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\10,08,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5CCA4D-E9FD-4393-A255-556573A3133B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6D6BE4-1E34-4ED8-AEDA-58051290BC5A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AH$120</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="186">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -663,6 +663,9 @@
   <si>
     <t>7156 СЕРВЕЛАТ КОПЧ.НА БУКЕ в/к в/у 0.35кг_50с</t>
   </si>
+  <si>
+    <t>08,08,26 списано 35 шт.</t>
+  </si>
 </sst>
 </file>
 
@@ -7440,7 +7443,9 @@
       <c r="AF56" s="1">
         <v>4.2</v>
       </c>
-      <c r="AG56" s="1"/>
+      <c r="AG56" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="AH56" s="1">
         <f t="shared" si="7"/>
         <v>12.959999999999999</v>
